--- a/branches/sandbox/ValueSet-PathogenicAgentHPV.xlsx
+++ b/branches/sandbox/ValueSet-PathogenicAgentHPV.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-03-11T13:27:28+00:00</t>
+    <t>2025-03-11T13:28:38+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/sandbox/ValueSet-PathogenicAgentHPV.xlsx
+++ b/branches/sandbox/ValueSet-PathogenicAgentHPV.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-03-11T13:28:38+00:00</t>
+    <t>2025-03-11T13:29:42+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
